--- a/survey_templates/043_intimacy_expectations_survey--survey_templates.xlsx
+++ b/survey_templates/043_intimacy_expectations_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_relationship'}</t>
+          <t>in_a_relationship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'In a relationship'}</t>
+          <t>In a relationship</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_long-term_relationship'}</t>
+          <t>in_a_long-term_relationship</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'In a long-term relationship'}</t>
+          <t>In a long-term relationship</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_marriage'}</t>
+          <t>in_a_marriage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'In a marriage'}</t>
+          <t>In a marriage</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_long-term_partnership'}</t>
+          <t>in_a_long-term_partnership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In a long-term partnership'}</t>
+          <t>In a long-term partnership</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'in_a_domestic_partnership'}</t>
+          <t>in_a_domestic_partnership</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'In a domestic partnership'}</t>
+          <t>In a domestic partnership</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'physical_touch'}</t>
+          <t>physical_touch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Physical touch'}</t>
+          <t>Physical touch</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_intimacy'}</t>
+          <t>emotional_intimacy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional intimacy'}</t>
+          <t>Emotional intimacy</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'financial_support'}</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Financial support'}</t>
+          <t>Financial support</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_support'}</t>
+          <t>emotional_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional support'}</t>
+          <t>Emotional support</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no_boundaries'}</t>
+          <t>no_boundaries</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No boundaries'}</t>
+          <t>No boundaries</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'some_boundaries'}</t>
+          <t>some_boundaries</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Some boundaries'}</t>
+          <t>Some boundaries</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'physical_boundaries_(e.g._no_kissing,_no_touching)'}</t>
+          <t>physical_boundaries_(e.g._no_kissing,_no_touching)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Physical boundaries (e.g. no kissing, no touching)'}</t>
+          <t>Physical boundaries (e.g. no kissing, no touching)</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_boundaries_(e.g._no_talking_about_feelings,_no_emotional_support)'}</t>
+          <t>emotional_boundaries_(e.g._no_talking_about_feelings,_no_emotional_support)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional boundaries (e.g. no talking about feelings, no emotional support)'}</t>
+          <t>Emotional boundaries (e.g. no talking about feelings, no emotional support)</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_support'}</t>
+          <t>emotional_support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional support'}</t>
+          <t>Emotional support</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'financial_support'}</t>
+          <t>financial_support</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Financial support'}</t>
+          <t>Financial support</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'physical_support'}</t>
+          <t>physical_support</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Physical support'}</t>
+          <t>Physical support</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'intellectual_support'}</t>
+          <t>intellectual_support</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Intellectual support'}</t>
+          <t>Intellectual support</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'open_and_direct'}</t>
+          <t>open_and_direct</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Open and direct'}</t>
+          <t>Open and direct</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'indirect_and_sensitive'}</t>
+          <t>indirect_and_sensitive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Indirect and sensitive'}</t>
+          <t>Indirect and sensitive</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'avoiding_conflict'}</t>
+          <t>avoiding_conflict</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Avoiding conflict'}</t>
+          <t>Avoiding conflict</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Text message'}</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'in-person_conversation'}</t>
+          <t>in-person_conversation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'In-person conversation'}</t>
+          <t>In-person conversation</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Video call'}</t>
+          <t>Video call</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'openly'}</t>
+          <t>openly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Openly'}</t>
+          <t>Openly</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'indirectly'}</t>
+          <t>indirectly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Indirectly'}</t>
+          <t>Indirectly</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'directly'}</t>
+          <t>directly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Directly'}</t>
+          <t>Directly</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'indirectly'}</t>
+          <t>indirectly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Indirectly'}</t>
+          <t>Indirectly</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'avoiding'}</t>
+          <t>avoiding</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Avoiding'}</t>
+          <t>Avoiding</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'constantly'}</t>
+          <t>constantly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Constantly'}</t>
+          <t>Constantly</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'directly'}</t>
+          <t>directly</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Directly'}</t>
+          <t>Directly</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'indirectly'}</t>
+          <t>indirectly</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Indirectly'}</t>
+          <t>Indirectly</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'avoiding'}</t>
+          <t>avoiding</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Avoiding'}</t>
+          <t>Avoiding</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2392,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'label':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'label': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'label':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'label': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'label':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'label': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'label':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'label': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'label':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'label': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
